--- a/ig/ch-elm/StructureDefinition-ch-elm-observation-results-laboratory-susceptibility-strict.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-observation-results-laboratory-susceptibility-strict.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -383,7 +383,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -809,7 +809,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -838,7 +838,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -924,7 +924,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
@@ -1100,7 +1100,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1145,7 +1145,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1168,7 +1168,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1519,7 +1519,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1548,7 +1548,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1607,7 +1607,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1678,7 +1678,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1758,7 +1758,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1808,7 +1808,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1841,7 +1841,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1900,7 +1900,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1985,7 +1985,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -2035,7 +2035,7 @@
     <t>Observation.component.value[x]:valueCodeableConcept</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
+    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips|2.0.0}
 </t>
   </si>
   <si>

--- a/ig/ch-elm/StructureDefinition-ch-elm-observation-results-laboratory-susceptibility-strict.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-observation-results-laboratory-susceptibility-strict.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-observation-results-laboratory-susceptibility-strict.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-observation-results-laboratory-susceptibility-strict.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-observation-results-laboratory-susceptibility-strict.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-observation-results-laboratory-susceptibility-strict.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
